--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week02_07Sep.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week02_07Sep.xlsx
@@ -148,7 +148,7 @@
   </si>
   <si>
     <t xml:space="preserve">Teacher modelling of comparison and rounding strategies. Regular use of mathematical vocabulary. Practical resources available throughout lessons.  Ongoing assessment through questioning, observation and discussion.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: next task adapted; who needs the method re-modelled shapes grouping and the half-termly plan [NS].</t>
@@ -203,7 +203,7 @@
   </si>
   <si>
     <t xml:space="preserve">TA supports the matching activity and the charter vote.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: the W7 pitch shapes the W8 real action; outcomes feed APDR and the citizenship ladder [NS].</t>
